--- a/logs/logs_feb.xlsx
+++ b/logs/logs_feb.xlsx
@@ -480,7 +480,7 @@
         <v>46023</v>
       </c>
       <c r="C2" t="n">
-        <v>762.2</v>
+        <v>758.1</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
@@ -490,10 +490,10 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1257630</v>
+        <v>1250865</v>
       </c>
       <c r="H2" t="n">
-        <v>-449730</v>
+        <v>-420415</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -513,28 +513,28 @@
         <v>46024</v>
       </c>
       <c r="C3" t="n">
-        <v>764.8</v>
+        <v>761.95</v>
       </c>
       <c r="D3" t="n">
-        <v>762.2</v>
+        <v>758.1</v>
       </c>
       <c r="E3" t="n">
-        <v>2.599999999999909</v>
+        <v>3.850000000000023</v>
       </c>
       <c r="F3" t="n">
-        <v>2179891.999999924</v>
+        <v>21175.00000000012</v>
       </c>
       <c r="G3" t="n">
-        <v>3437521.999999924</v>
+        <v>1272040</v>
       </c>
       <c r="H3" t="n">
-        <v>-449730</v>
+        <v>-420415</v>
       </c>
       <c r="I3" t="n">
-        <v>2179891.999999924</v>
+        <v>21175.00000000023</v>
       </c>
       <c r="J3" t="n">
-        <v>-115.7687622303027</v>
+        <v>-108.2225427991299</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -548,28 +548,28 @@
         <v>46027</v>
       </c>
       <c r="C4" t="n">
-        <v>772.4</v>
+        <v>767.15</v>
       </c>
       <c r="D4" t="n">
-        <v>764.8</v>
+        <v>761.95</v>
       </c>
       <c r="E4" t="n">
-        <v>7.600000000000023</v>
+        <v>5.199999999999932</v>
       </c>
       <c r="F4" t="n">
-        <v>6371992.000000019</v>
+        <v>28599.99999999963</v>
       </c>
       <c r="G4" t="n">
-        <v>9809513.999999942</v>
+        <v>1300640</v>
       </c>
       <c r="H4" t="n">
-        <v>-449730</v>
+        <v>-420415</v>
       </c>
       <c r="I4" t="n">
-        <v>8551883.999999942</v>
+        <v>49774.99999999977</v>
       </c>
       <c r="J4" t="n">
-        <v>202.3178040951231</v>
+        <v>-105.1327186051142</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -583,28 +583,28 @@
         <v>46028</v>
       </c>
       <c r="C5" t="n">
-        <v>787.65</v>
+        <v>783.7</v>
       </c>
       <c r="D5" t="n">
-        <v>772.4</v>
+        <v>767.15</v>
       </c>
       <c r="E5" t="n">
-        <v>15.25</v>
+        <v>16.55000000000007</v>
       </c>
       <c r="F5" t="n">
-        <v>12785905</v>
+        <v>91025.00000000038</v>
       </c>
       <c r="G5" t="n">
-        <v>22595418.99999994</v>
+        <v>1391665</v>
       </c>
       <c r="H5" t="n">
-        <v>-449730</v>
+        <v>-420415</v>
       </c>
       <c r="I5" t="n">
-        <v>21337788.99999994</v>
+        <v>140800.0000000002</v>
       </c>
       <c r="J5" t="n">
-        <v>1132.109305661788</v>
+        <v>-100.9594495638464</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -618,28 +618,28 @@
         <v>46029</v>
       </c>
       <c r="C6" t="n">
-        <v>784.35</v>
+        <v>780</v>
       </c>
       <c r="D6" t="n">
-        <v>787.65</v>
+        <v>783.7</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.299999999999955</v>
+        <v>-3.700000000000045</v>
       </c>
       <c r="F6" t="n">
-        <v>-2766785.999999962</v>
+        <v>-20350.00000000025</v>
       </c>
       <c r="G6" t="n">
-        <v>19828632.99999998</v>
+        <v>1371315</v>
       </c>
       <c r="H6" t="n">
-        <v>-449730</v>
+        <v>-420415</v>
       </c>
       <c r="I6" t="n">
-        <v>18571002.99999998</v>
+        <v>120450</v>
       </c>
       <c r="J6" t="n">
-        <v>2997.809358147523</v>
+        <v>-87.67721828827268</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -653,28 +653,28 @@
         <v>46030</v>
       </c>
       <c r="C7" t="n">
-        <v>770.5</v>
+        <v>765.9</v>
       </c>
       <c r="D7" t="n">
-        <v>784.35</v>
+        <v>780</v>
       </c>
       <c r="E7" t="n">
-        <v>-13.85000000000002</v>
+        <v>-14.10000000000002</v>
       </c>
       <c r="F7" t="n">
-        <v>-11612117.00000002</v>
+        <v>-77550.00000000013</v>
       </c>
       <c r="G7" t="n">
-        <v>8216515.999999959</v>
+        <v>1293765</v>
       </c>
       <c r="H7" t="n">
-        <v>-449730</v>
+        <v>-420415</v>
       </c>
       <c r="I7" t="n">
-        <v>6958885.999999959</v>
+        <v>42899.99999999977</v>
       </c>
       <c r="J7" t="n">
-        <v>2594.08410088832</v>
+        <v>-90.64665972148254</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -688,31 +688,31 @@
         <v>46031</v>
       </c>
       <c r="C8" t="n">
-        <v>760.25</v>
+        <v>755.3</v>
       </c>
       <c r="D8" t="n">
-        <v>770.5</v>
+        <v>765.9</v>
       </c>
       <c r="E8" t="n">
-        <v>-10.25</v>
+        <v>-10.60000000000002</v>
       </c>
       <c r="F8" t="n">
-        <v>-8593805</v>
+        <v>-58300.00000000012</v>
       </c>
       <c r="G8" t="n">
-        <v>1257630</v>
+        <v>1235465</v>
       </c>
       <c r="H8" t="n">
-        <v>-2084649.000000041</v>
+        <v>-420415</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>899.6614302701247</v>
+        <v>-101.9626392372281</v>
       </c>
       <c r="K8" t="n">
-        <v>1634919.000000041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -723,28 +723,28 @@
         <v>46034</v>
       </c>
       <c r="C9" t="n">
-        <v>767.2</v>
+        <v>761.75</v>
       </c>
       <c r="D9" t="n">
-        <v>760.25</v>
+        <v>755.3</v>
       </c>
       <c r="E9" t="n">
-        <v>6.950000000000045</v>
+        <v>6.450000000000045</v>
       </c>
       <c r="F9" t="n">
-        <v>5827019.000000038</v>
+        <v>35475.00000000025</v>
       </c>
       <c r="G9" t="n">
-        <v>7084649.000000038</v>
+        <v>1270940</v>
       </c>
       <c r="H9" t="n">
-        <v>-2084649.000000041</v>
+        <v>-420415</v>
       </c>
       <c r="I9" t="n">
-        <v>5827019.000000038</v>
+        <v>20074.99999999977</v>
       </c>
       <c r="J9" t="n">
-        <v>-536.6269415307917</v>
+        <v>-108.2225427991299</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -758,28 +758,28 @@
         <v>46035</v>
       </c>
       <c r="C10" t="n">
-        <v>761.15</v>
+        <v>755.9</v>
       </c>
       <c r="D10" t="n">
-        <v>767.2</v>
+        <v>761.75</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.050000000000068</v>
+        <v>-5.850000000000023</v>
       </c>
       <c r="F10" t="n">
-        <v>-5072441.000000057</v>
+        <v>-32175.00000000012</v>
       </c>
       <c r="G10" t="n">
-        <v>2012207.999999981</v>
+        <v>1238765</v>
       </c>
       <c r="H10" t="n">
-        <v>-2084649.000000041</v>
+        <v>-420415</v>
       </c>
       <c r="I10" t="n">
-        <v>754577.9999999814</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>313.6429184545165</v>
+        <v>-105.2932289528554</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -793,31 +793,31 @@
         <v>46036</v>
       </c>
       <c r="C11" t="n">
-        <v>754.6</v>
+        <v>749.9</v>
       </c>
       <c r="D11" t="n">
-        <v>761.15</v>
+        <v>755.9</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.549999999999955</v>
+        <v>-6</v>
       </c>
       <c r="F11" t="n">
-        <v>-5491650.999999962</v>
+        <v>-33000</v>
       </c>
       <c r="G11" t="n">
-        <v>1257630</v>
+        <v>1205765</v>
       </c>
       <c r="H11" t="n">
-        <v>-6821722.000000021</v>
+        <v>-420415</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-426.5200531873739</v>
+        <v>-108.2225427991299</v>
       </c>
       <c r="K11" t="n">
-        <v>4737072.99999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -828,31 +828,31 @@
         <v>46038</v>
       </c>
       <c r="C12" t="n">
-        <v>743.35</v>
+        <v>738.4</v>
       </c>
       <c r="D12" t="n">
-        <v>754.6</v>
+        <v>749.9</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.25</v>
+        <v>-11.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-9432225</v>
+        <v>-63250</v>
       </c>
       <c r="G12" t="n">
-        <v>1257630</v>
+        <v>1142515</v>
       </c>
       <c r="H12" t="n">
-        <v>-16253947.00000002</v>
+        <v>-420415</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-1756.036537965506</v>
+        <v>-108.2225427991299</v>
       </c>
       <c r="K12" t="n">
-        <v>9432225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -863,28 +863,28 @@
         <v>46041</v>
       </c>
       <c r="C13" t="n">
-        <v>746.65</v>
+        <v>742.45</v>
       </c>
       <c r="D13" t="n">
-        <v>743.35</v>
+        <v>738.4</v>
       </c>
       <c r="E13" t="n">
-        <v>3.299999999999955</v>
+        <v>4.050000000000068</v>
       </c>
       <c r="F13" t="n">
-        <v>2766785.999999962</v>
+        <v>22275.00000000037</v>
       </c>
       <c r="G13" t="n">
-        <v>4024415.999999962</v>
+        <v>1164790</v>
       </c>
       <c r="H13" t="n">
-        <v>-16253947.00000002</v>
+        <v>-420415</v>
       </c>
       <c r="I13" t="n">
-        <v>2766785.999999962</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-4184.064495468268</v>
+        <v>-108.2225427991299</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -898,31 +898,31 @@
         <v>46042</v>
       </c>
       <c r="C14" t="n">
-        <v>740.35</v>
+        <v>736</v>
       </c>
       <c r="D14" t="n">
-        <v>746.65</v>
+        <v>742.45</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.299999999999955</v>
+        <v>-6.450000000000045</v>
       </c>
       <c r="F14" t="n">
-        <v>-5282045.999999962</v>
+        <v>-35475.00000000025</v>
       </c>
       <c r="G14" t="n">
-        <v>1257630</v>
+        <v>1129315</v>
       </c>
       <c r="H14" t="n">
-        <v>-18769207.00000002</v>
+        <v>-420415</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-3780.339238209065</v>
+        <v>-108.2225427991299</v>
       </c>
       <c r="K14" t="n">
-        <v>2515260</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -933,31 +933,31 @@
         <v>46043</v>
       </c>
       <c r="C15" t="n">
-        <v>731.8</v>
+        <v>729.6</v>
       </c>
       <c r="D15" t="n">
-        <v>740.35</v>
+        <v>736</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.550000000000068</v>
+        <v>-6.399999999999977</v>
       </c>
       <c r="F15" t="n">
-        <v>-7168491.000000057</v>
+        <v>-35199.99999999988</v>
       </c>
       <c r="G15" t="n">
-        <v>1257630</v>
+        <v>1094115</v>
       </c>
       <c r="H15" t="n">
-        <v>-25937698.00000008</v>
+        <v>-420415</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-4831.538617469004</v>
+        <v>-108.2225427991299</v>
       </c>
       <c r="K15" t="n">
-        <v>7168491.000000057</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -968,28 +968,28 @@
         <v>46044</v>
       </c>
       <c r="C16" t="n">
-        <v>733</v>
+        <v>728.8</v>
       </c>
       <c r="D16" t="n">
-        <v>731.8</v>
+        <v>729.6</v>
       </c>
       <c r="E16" t="n">
-        <v>1.200000000000045</v>
+        <v>-0.8000000000000682</v>
       </c>
       <c r="F16" t="n">
-        <v>1006104.000000038</v>
+        <v>-4400.000000000375</v>
       </c>
       <c r="G16" t="n">
-        <v>2263734.000000038</v>
+        <v>1089715</v>
       </c>
       <c r="H16" t="n">
-        <v>-25937698.00000008</v>
+        <v>-420415</v>
       </c>
       <c r="I16" t="n">
-        <v>1006104.000000038</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-6676.839865171116</v>
+        <v>-108.2225427991299</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1003,31 +1003,31 @@
         <v>46045</v>
       </c>
       <c r="C17" t="n">
-        <v>718.7</v>
+        <v>714.1</v>
       </c>
       <c r="D17" t="n">
-        <v>733</v>
+        <v>728.8</v>
       </c>
       <c r="E17" t="n">
-        <v>-14.29999999999995</v>
+        <v>-14.69999999999993</v>
       </c>
       <c r="F17" t="n">
-        <v>-11989405.99999996</v>
+        <v>-80849.99999999962</v>
       </c>
       <c r="G17" t="n">
-        <v>1257630</v>
+        <v>1008865</v>
       </c>
       <c r="H17" t="n">
-        <v>-36921000</v>
+        <v>-420415</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-6530.030680713216</v>
+        <v>-108.2225427991299</v>
       </c>
       <c r="K17" t="n">
-        <v>10983301.99999993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1038,28 +1038,28 @@
         <v>46049</v>
       </c>
       <c r="C18" t="n">
-        <v>728.9</v>
+        <v>724.4</v>
       </c>
       <c r="D18" t="n">
-        <v>718.7</v>
+        <v>714.1</v>
       </c>
       <c r="E18" t="n">
-        <v>10.19999999999993</v>
+        <v>10.29999999999995</v>
       </c>
       <c r="F18" t="n">
-        <v>8551883.999999942</v>
+        <v>56649.99999999975</v>
       </c>
       <c r="G18" t="n">
-        <v>9809513.999999942</v>
+        <v>1065515</v>
       </c>
       <c r="H18" t="n">
-        <v>-36921000</v>
+        <v>-420415</v>
       </c>
       <c r="I18" t="n">
-        <v>8551883.999999942</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-9504.143531240978</v>
+        <v>-108.2225427991299</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1073,28 +1073,28 @@
         <v>46050</v>
       </c>
       <c r="C19" t="n">
-        <v>735.4</v>
+        <v>730.5</v>
       </c>
       <c r="D19" t="n">
-        <v>728.9</v>
+        <v>724.4</v>
       </c>
       <c r="E19" t="n">
-        <v>6.5</v>
+        <v>6.100000000000023</v>
       </c>
       <c r="F19" t="n">
-        <v>5449730</v>
+        <v>33550.00000000012</v>
       </c>
       <c r="G19" t="n">
-        <v>15259243.99999994</v>
+        <v>1099065</v>
       </c>
       <c r="H19" t="n">
-        <v>-36921000</v>
+        <v>-420415</v>
       </c>
       <c r="I19" t="n">
-        <v>14001613.99999994</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-8256.265463348887</v>
+        <v>-108.2225427991299</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1108,28 +1108,28 @@
         <v>46051</v>
       </c>
       <c r="C20" t="n">
-        <v>733.45</v>
+        <v>729.3</v>
       </c>
       <c r="D20" t="n">
-        <v>735.4</v>
+        <v>730.5</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.949999999999932</v>
+        <v>-1.200000000000045</v>
       </c>
       <c r="F20" t="n">
-        <v>-1634918.999999943</v>
+        <v>-6600.00000000025</v>
       </c>
       <c r="G20" t="n">
-        <v>13624325</v>
+        <v>1092465</v>
       </c>
       <c r="H20" t="n">
-        <v>-36921000</v>
+        <v>-420415</v>
       </c>
       <c r="I20" t="n">
-        <v>12366695</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-7461.049047535294</v>
+        <v>-108.2225427991299</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1143,28 +1143,28 @@
         <v>46052</v>
       </c>
       <c r="C21" t="n">
-        <v>737.45</v>
+        <v>733.5</v>
       </c>
       <c r="D21" t="n">
-        <v>733.45</v>
+        <v>729.3</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>4.200000000000045</v>
       </c>
       <c r="F21" t="n">
-        <v>3353680</v>
+        <v>23100.00000000025</v>
       </c>
       <c r="G21" t="n">
-        <v>16978005</v>
+        <v>1115565</v>
       </c>
       <c r="H21" t="n">
-        <v>-36921000</v>
+        <v>-420415</v>
       </c>
       <c r="I21" t="n">
-        <v>15720375</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-7699.613972279364</v>
+        <v>-108.2225427991299</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>

--- a/logs/logs_feb.xlsx
+++ b/logs/logs_feb.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,15 +458,10 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Interest_Profit</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
           <t>Interest_Flow</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Margin_call</t>
         </is>
@@ -490,18 +485,15 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1250865</v>
+        <v>4252941</v>
       </c>
       <c r="H2" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -522,21 +514,18 @@
         <v>3.850000000000023</v>
       </c>
       <c r="F3" t="n">
-        <v>21175.00000000012</v>
+        <v>71995.00000000042</v>
       </c>
       <c r="G3" t="n">
-        <v>1272040</v>
+        <v>4324936</v>
       </c>
       <c r="H3" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>21175.00000000023</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-108.2225427991299</v>
-      </c>
-      <c r="K3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -557,21 +546,18 @@
         <v>5.199999999999932</v>
       </c>
       <c r="F4" t="n">
-        <v>28599.99999999963</v>
+        <v>97239.99999999872</v>
       </c>
       <c r="G4" t="n">
-        <v>1300640</v>
+        <v>4422175.999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>49774.99999999977</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-105.1327186051142</v>
-      </c>
-      <c r="K4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -592,21 +578,18 @@
         <v>16.55000000000007</v>
       </c>
       <c r="F5" t="n">
-        <v>91025.00000000038</v>
+        <v>309485.0000000013</v>
       </c>
       <c r="G5" t="n">
-        <v>1391665</v>
+        <v>4731661</v>
       </c>
       <c r="H5" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>140800.0000000002</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-100.9594495638464</v>
-      </c>
-      <c r="K5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -627,21 +610,18 @@
         <v>-3.700000000000045</v>
       </c>
       <c r="F6" t="n">
-        <v>-20350.00000000025</v>
+        <v>-69190.00000000084</v>
       </c>
       <c r="G6" t="n">
-        <v>1371315</v>
+        <v>4662470.999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>120450</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-87.67721828827268</v>
-      </c>
-      <c r="K6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -662,21 +642,18 @@
         <v>-14.10000000000002</v>
       </c>
       <c r="F7" t="n">
-        <v>-77550.00000000013</v>
+        <v>-263670.0000000004</v>
       </c>
       <c r="G7" t="n">
-        <v>1293765</v>
+        <v>4398800.999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>42899.99999999977</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-90.64665972148254</v>
-      </c>
-      <c r="K7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -697,21 +674,18 @@
         <v>-10.60000000000002</v>
       </c>
       <c r="F8" t="n">
-        <v>-58300.00000000012</v>
+        <v>-198220.0000000004</v>
       </c>
       <c r="G8" t="n">
-        <v>1235465</v>
+        <v>4200580.999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-101.9626392372281</v>
-      </c>
-      <c r="K8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -732,21 +706,18 @@
         <v>6.450000000000045</v>
       </c>
       <c r="F9" t="n">
-        <v>35475.00000000025</v>
+        <v>120615.0000000008</v>
       </c>
       <c r="G9" t="n">
-        <v>1270940</v>
+        <v>4321196</v>
       </c>
       <c r="H9" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>20074.99999999977</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-108.2225427991299</v>
-      </c>
-      <c r="K9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -767,21 +738,18 @@
         <v>-5.850000000000023</v>
       </c>
       <c r="F10" t="n">
-        <v>-32175.00000000012</v>
+        <v>-109395.0000000004</v>
       </c>
       <c r="G10" t="n">
-        <v>1238765</v>
+        <v>4211801</v>
       </c>
       <c r="H10" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-105.2932289528554</v>
-      </c>
-      <c r="K10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -802,21 +770,18 @@
         <v>-6</v>
       </c>
       <c r="F11" t="n">
-        <v>-33000</v>
+        <v>-112200</v>
       </c>
       <c r="G11" t="n">
-        <v>1205765</v>
+        <v>4099601</v>
       </c>
       <c r="H11" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-108.2225427991299</v>
-      </c>
-      <c r="K11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -837,21 +802,18 @@
         <v>-11.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-63250</v>
+        <v>-215050</v>
       </c>
       <c r="G12" t="n">
-        <v>1142515</v>
+        <v>3884551</v>
       </c>
       <c r="H12" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-108.2225427991299</v>
-      </c>
-      <c r="K12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -872,21 +834,18 @@
         <v>4.050000000000068</v>
       </c>
       <c r="F13" t="n">
-        <v>22275.00000000037</v>
+        <v>75735.00000000128</v>
       </c>
       <c r="G13" t="n">
-        <v>1164790</v>
+        <v>3960286.000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-108.2225427991299</v>
-      </c>
-      <c r="K13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -907,21 +866,18 @@
         <v>-6.450000000000045</v>
       </c>
       <c r="F14" t="n">
-        <v>-35475.00000000025</v>
+        <v>-120615.0000000008</v>
       </c>
       <c r="G14" t="n">
-        <v>1129315</v>
+        <v>3839671</v>
       </c>
       <c r="H14" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-108.2225427991299</v>
-      </c>
-      <c r="K14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -942,21 +898,18 @@
         <v>-6.399999999999977</v>
       </c>
       <c r="F15" t="n">
-        <v>-35199.99999999988</v>
+        <v>-119679.9999999996</v>
       </c>
       <c r="G15" t="n">
-        <v>1094115</v>
+        <v>3719991.000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-108.2225427991299</v>
-      </c>
-      <c r="K15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -977,21 +930,18 @@
         <v>-0.8000000000000682</v>
       </c>
       <c r="F16" t="n">
-        <v>-4400.000000000375</v>
+        <v>-14960.00000000128</v>
       </c>
       <c r="G16" t="n">
-        <v>1089715</v>
+        <v>3705031</v>
       </c>
       <c r="H16" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-108.2225427991299</v>
-      </c>
-      <c r="K16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1012,21 +962,18 @@
         <v>-14.69999999999993</v>
       </c>
       <c r="F17" t="n">
-        <v>-80849.99999999962</v>
+        <v>-274889.9999999987</v>
       </c>
       <c r="G17" t="n">
-        <v>1008865</v>
+        <v>3430141.000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-108.2225427991299</v>
-      </c>
-      <c r="K17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1047,21 +994,18 @@
         <v>10.29999999999995</v>
       </c>
       <c r="F18" t="n">
-        <v>56649.99999999975</v>
+        <v>192609.9999999992</v>
       </c>
       <c r="G18" t="n">
-        <v>1065515</v>
+        <v>3622751</v>
       </c>
       <c r="H18" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-108.2225427991299</v>
-      </c>
-      <c r="K18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1082,21 +1026,18 @@
         <v>6.100000000000023</v>
       </c>
       <c r="F19" t="n">
-        <v>33550.00000000012</v>
+        <v>114070.0000000004</v>
       </c>
       <c r="G19" t="n">
-        <v>1099065</v>
+        <v>3736821</v>
       </c>
       <c r="H19" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-108.2225427991299</v>
-      </c>
-      <c r="K19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1117,21 +1058,18 @@
         <v>-1.200000000000045</v>
       </c>
       <c r="F20" t="n">
-        <v>-6600.00000000025</v>
+        <v>-22440.00000000085</v>
       </c>
       <c r="G20" t="n">
-        <v>1092465</v>
+        <v>3714381</v>
       </c>
       <c r="H20" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-108.2225427991299</v>
-      </c>
-      <c r="K20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1152,21 +1090,18 @@
         <v>4.200000000000045</v>
       </c>
       <c r="F21" t="n">
-        <v>23100.00000000025</v>
+        <v>78540.00000000084</v>
       </c>
       <c r="G21" t="n">
-        <v>1115565</v>
+        <v>3792921</v>
       </c>
       <c r="H21" t="n">
-        <v>-420415</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-108.2225427991299</v>
-      </c>
-      <c r="K21" t="n">
         <v>0</v>
       </c>
     </row>
